--- a/VerveStacks_GBR/vt_vervestacks_GBR_v1.xlsx
+++ b/VerveStacks_GBR/vt_vervestacks_GBR_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GBR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABB6204A-3A3A-40AC-A99E-0D7F22E23B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{026CE642-B3C0-48EE-9DEA-467AC34CE3AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B035E829-E450-4E9C-9DDB-18D2EFC76137}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2F4583FA-BDD0-43F4-8C66-F5877FA06B61}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3973,7 +3973,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22DFF85A-2AAD-4D91-981B-1C65C454BEA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F39D7540-FDB1-484B-84A4-0DC491F893B5}">
   <dimension ref="B9:T158"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12302,7 +12302,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E28263A-F51E-47E9-8485-D33EF3B96E8A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{264D6273-DCDE-48A2-9F0E-304D2624E41C}">
   <dimension ref="B9:T213"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23369,7 +23369,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BCDFFB6-2617-4624-8386-3BCDE7B3E432}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C38526E8-6F9E-4DA1-B69D-66D73299D519}">
   <dimension ref="B9:T683"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -29505,7 +29505,7 @@
         <v>129</v>
       </c>
       <c r="P125" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q125" t="s">
         <v>336</v>
@@ -29558,7 +29558,7 @@
         <v>129</v>
       </c>
       <c r="P126" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q126" t="s">
         <v>336</v>
@@ -32302,7 +32302,7 @@
         <v>189</v>
       </c>
       <c r="P178" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q178" t="s">
         <v>336</v>
@@ -32352,7 +32352,7 @@
         <v>189</v>
       </c>
       <c r="P179" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q179" t="s">
         <v>336</v>
@@ -32402,7 +32402,7 @@
         <v>191</v>
       </c>
       <c r="P180" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q180" t="s">
         <v>336</v>
@@ -32455,7 +32455,7 @@
         <v>191</v>
       </c>
       <c r="P181" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q181" t="s">
         <v>336</v>
@@ -32508,7 +32508,7 @@
         <v>193</v>
       </c>
       <c r="P182" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q182" t="s">
         <v>336</v>
@@ -32561,7 +32561,7 @@
         <v>193</v>
       </c>
       <c r="P183" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q183" t="s">
         <v>336</v>
@@ -32720,7 +32720,7 @@
         <v>197</v>
       </c>
       <c r="P186" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q186" t="s">
         <v>336</v>
@@ -32773,7 +32773,7 @@
         <v>197</v>
       </c>
       <c r="P187" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q187" t="s">
         <v>336</v>
@@ -32932,7 +32932,7 @@
         <v>200</v>
       </c>
       <c r="P190" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q190" t="s">
         <v>336</v>
@@ -32985,7 +32985,7 @@
         <v>200</v>
       </c>
       <c r="P191" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q191" t="s">
         <v>336</v>
@@ -33144,7 +33144,7 @@
         <v>203</v>
       </c>
       <c r="P194" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q194" t="s">
         <v>336</v>
@@ -33197,7 +33197,7 @@
         <v>203</v>
       </c>
       <c r="P195" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q195" t="s">
         <v>336</v>
@@ -33409,7 +33409,7 @@
         <v>209</v>
       </c>
       <c r="P199" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q199" t="s">
         <v>336</v>
@@ -33462,7 +33462,7 @@
         <v>209</v>
       </c>
       <c r="P200" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q200" t="s">
         <v>336</v>
@@ -36355,7 +36355,7 @@
         <v>284</v>
       </c>
       <c r="P253" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q253" t="s">
         <v>336</v>
@@ -36411,7 +36411,7 @@
         <v>284</v>
       </c>
       <c r="P254" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q254" t="s">
         <v>336</v>
@@ -36859,7 +36859,7 @@
         <v>298</v>
       </c>
       <c r="P262" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q262" t="s">
         <v>336</v>
@@ -36915,7 +36915,7 @@
         <v>298</v>
       </c>
       <c r="P263" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q263" t="s">
         <v>336</v>
@@ -37699,7 +37699,7 @@
         <v>315</v>
       </c>
       <c r="P277" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q277" t="s">
         <v>336</v>
@@ -37755,7 +37755,7 @@
         <v>315</v>
       </c>
       <c r="P278" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q278" t="s">
         <v>336</v>
@@ -40310,7 +40310,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L345">
-        <v>0.55373821771400933</v>
+        <v>0.55373821771400944</v>
       </c>
     </row>
     <row r="346" spans="2:12" x14ac:dyDescent="0.45">
@@ -40333,7 +40333,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L346">
-        <v>0.55373821771400933</v>
+        <v>0.55373821771400944</v>
       </c>
     </row>
     <row r="347" spans="2:12" x14ac:dyDescent="0.45">
@@ -40356,7 +40356,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L347">
-        <v>0.55373821771400933</v>
+        <v>0.55373821771400944</v>
       </c>
     </row>
     <row r="348" spans="2:12" x14ac:dyDescent="0.45">
@@ -52089,7 +52089,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1C7D971-C500-4F75-A553-3154598089C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6008BEE9-E41A-40BF-B8D0-7FE859A1CEAF}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_GBR/vt_vervestacks_GBR_v1.xlsx
+++ b/VerveStacks_GBR/vt_vervestacks_GBR_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GBR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{026CE642-B3C0-48EE-9DEA-467AC34CE3AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35985C12-E8B6-4AFF-A4A1-D0DED2E2D576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2F4583FA-BDD0-43F4-8C66-F5877FA06B61}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D5BC3DE1-3DA8-4196-88EA-F8B2368484C8}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3973,7 +3973,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F39D7540-FDB1-484B-84A4-0DC491F893B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36292FE9-4648-43D0-9DD4-7EAA511F1FE9}">
   <dimension ref="B9:T158"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5900,7 +5900,7 @@
         <v>14</v>
       </c>
       <c r="E44">
-        <v>0.10069392000000002</v>
+        <v>8.0555136000000027E-2</v>
       </c>
       <c r="F44">
         <v>3583</v>
@@ -5956,7 +5956,7 @@
         <v>14</v>
       </c>
       <c r="E45">
-        <v>0.46865000000000007</v>
+        <v>0.37492000000000003</v>
       </c>
       <c r="F45">
         <v>1365</v>
@@ -6012,7 +6012,7 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>0.46865000000000007</v>
+        <v>0.37492000000000003</v>
       </c>
       <c r="F46">
         <v>1365</v>
@@ -6068,7 +6068,7 @@
         <v>14</v>
       </c>
       <c r="E47">
-        <v>0.46865000000000007</v>
+        <v>0.37492000000000003</v>
       </c>
       <c r="F47">
         <v>1365</v>
@@ -6124,7 +6124,7 @@
         <v>14</v>
       </c>
       <c r="E48">
-        <v>0.450625</v>
+        <v>0.36050000000000004</v>
       </c>
       <c r="F48">
         <v>1365</v>
@@ -6180,7 +6180,7 @@
         <v>14</v>
       </c>
       <c r="E49">
-        <v>0.52272499999999988</v>
+        <v>0.41817999999999989</v>
       </c>
       <c r="F49">
         <v>1365</v>
@@ -6236,7 +6236,7 @@
         <v>14</v>
       </c>
       <c r="E50">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F50">
         <v>1365</v>
@@ -6292,7 +6292,7 @@
         <v>14</v>
       </c>
       <c r="E51">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F51">
         <v>1365</v>
@@ -6348,7 +6348,7 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F52">
         <v>1365</v>
@@ -6404,7 +6404,7 @@
         <v>14</v>
       </c>
       <c r="E53">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F53">
         <v>1365</v>
@@ -6460,7 +6460,7 @@
         <v>14</v>
       </c>
       <c r="E54">
-        <v>0.49118125000000001</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F54">
         <v>1365</v>
@@ -6516,7 +6516,7 @@
         <v>14</v>
       </c>
       <c r="E55">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F55">
         <v>1365</v>
@@ -6572,7 +6572,7 @@
         <v>14</v>
       </c>
       <c r="E56">
-        <v>0.49118125000000001</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F56">
         <v>1365</v>
@@ -6628,7 +6628,7 @@
         <v>14</v>
       </c>
       <c r="E57">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F57">
         <v>1365</v>
@@ -6684,7 +6684,7 @@
         <v>14</v>
       </c>
       <c r="E58">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F58">
         <v>1365</v>
@@ -6740,7 +6740,7 @@
         <v>14</v>
       </c>
       <c r="E59">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F59">
         <v>1365</v>
@@ -6796,7 +6796,7 @@
         <v>14</v>
       </c>
       <c r="E60">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F60">
         <v>1365</v>
@@ -6852,7 +6852,7 @@
         <v>14</v>
       </c>
       <c r="E61">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F61">
         <v>1365</v>
@@ -6908,7 +6908,7 @@
         <v>14</v>
       </c>
       <c r="E62">
-        <v>0.450625</v>
+        <v>0.36050000000000004</v>
       </c>
       <c r="F62">
         <v>1365</v>
@@ -6964,7 +6964,7 @@
         <v>14</v>
       </c>
       <c r="E63">
-        <v>0.52272499999999988</v>
+        <v>0.41817999999999989</v>
       </c>
       <c r="F63">
         <v>1365</v>
@@ -7020,7 +7020,7 @@
         <v>14</v>
       </c>
       <c r="E64">
-        <v>0.52272499999999988</v>
+        <v>0.41817999999999989</v>
       </c>
       <c r="F64">
         <v>1365</v>
@@ -7076,7 +7076,7 @@
         <v>14</v>
       </c>
       <c r="E65">
-        <v>0.52272499999999988</v>
+        <v>0.41817999999999989</v>
       </c>
       <c r="F65">
         <v>1365</v>
@@ -7132,7 +7132,7 @@
         <v>14</v>
       </c>
       <c r="E66">
-        <v>0.46865000000000007</v>
+        <v>0.37492000000000003</v>
       </c>
       <c r="F66">
         <v>1365</v>
@@ -7188,7 +7188,7 @@
         <v>14</v>
       </c>
       <c r="E67">
-        <v>0.49118125000000001</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F67">
         <v>1365</v>
@@ -7244,7 +7244,7 @@
         <v>14</v>
       </c>
       <c r="E68">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000011</v>
       </c>
       <c r="F68">
         <v>1365</v>
@@ -7300,7 +7300,7 @@
         <v>14</v>
       </c>
       <c r="E69">
-        <v>0.54075000000000006</v>
+        <v>0.43260000000000004</v>
       </c>
       <c r="F69">
         <v>1365</v>
@@ -7356,7 +7356,7 @@
         <v>14</v>
       </c>
       <c r="E70">
-        <v>0.52272499999999988</v>
+        <v>0.41818</v>
       </c>
       <c r="F70">
         <v>1365</v>
@@ -7412,7 +7412,7 @@
         <v>14</v>
       </c>
       <c r="E71">
-        <v>0.49118125000000001</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F71">
         <v>1365</v>
@@ -7468,7 +7468,7 @@
         <v>14</v>
       </c>
       <c r="E72">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F72">
         <v>1365</v>
@@ -7524,7 +7524,7 @@
         <v>14</v>
       </c>
       <c r="E73">
-        <v>0.49118125000000001</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F73">
         <v>1365</v>
@@ -7580,7 +7580,7 @@
         <v>14</v>
       </c>
       <c r="E74">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F74">
         <v>1365</v>
@@ -7636,7 +7636,7 @@
         <v>14</v>
       </c>
       <c r="E75">
-        <v>0.52272499999999988</v>
+        <v>0.41818</v>
       </c>
       <c r="F75">
         <v>1365</v>
@@ -7692,7 +7692,7 @@
         <v>14</v>
       </c>
       <c r="E76">
-        <v>0.52272499999999988</v>
+        <v>0.41818</v>
       </c>
       <c r="F76">
         <v>1365</v>
@@ -7748,7 +7748,7 @@
         <v>14</v>
       </c>
       <c r="E77">
-        <v>0.52272499999999988</v>
+        <v>0.41818</v>
       </c>
       <c r="F77">
         <v>1365</v>
@@ -7804,7 +7804,7 @@
         <v>14</v>
       </c>
       <c r="E78">
-        <v>0.52272499999999988</v>
+        <v>0.41818</v>
       </c>
       <c r="F78">
         <v>1365</v>
@@ -7860,7 +7860,7 @@
         <v>14</v>
       </c>
       <c r="E79">
-        <v>0.52272499999999988</v>
+        <v>0.41818</v>
       </c>
       <c r="F79">
         <v>1365</v>
@@ -7916,7 +7916,7 @@
         <v>14</v>
       </c>
       <c r="E80">
-        <v>0.450625</v>
+        <v>0.36050000000000004</v>
       </c>
       <c r="F80">
         <v>1365</v>
@@ -7972,7 +7972,7 @@
         <v>14</v>
       </c>
       <c r="E81">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F81">
         <v>1365</v>
@@ -8028,7 +8028,7 @@
         <v>14</v>
       </c>
       <c r="E82">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F82">
         <v>1365</v>
@@ -8084,7 +8084,7 @@
         <v>14</v>
       </c>
       <c r="E83">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F83">
         <v>1365</v>
@@ -8140,7 +8140,7 @@
         <v>14</v>
       </c>
       <c r="E84">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F84">
         <v>1365</v>
@@ -8196,7 +8196,7 @@
         <v>14</v>
       </c>
       <c r="E85">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F85">
         <v>1365</v>
@@ -8252,7 +8252,7 @@
         <v>14</v>
       </c>
       <c r="E86">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F86">
         <v>1365</v>
@@ -8308,7 +8308,7 @@
         <v>14</v>
       </c>
       <c r="E87">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F87">
         <v>1365</v>
@@ -8364,7 +8364,7 @@
         <v>14</v>
       </c>
       <c r="E88">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F88">
         <v>1365</v>
@@ -8420,7 +8420,7 @@
         <v>14</v>
       </c>
       <c r="E89">
-        <v>0.49118125000000001</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F89">
         <v>1365</v>
@@ -8476,7 +8476,7 @@
         <v>14</v>
       </c>
       <c r="E90">
-        <v>0.52272499999999988</v>
+        <v>0.41818</v>
       </c>
       <c r="F90">
         <v>1365</v>
@@ -8532,7 +8532,7 @@
         <v>14</v>
       </c>
       <c r="E91">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F91">
         <v>1365</v>
@@ -8588,7 +8588,7 @@
         <v>14</v>
       </c>
       <c r="E92">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F92">
         <v>1365</v>
@@ -8644,7 +8644,7 @@
         <v>14</v>
       </c>
       <c r="E93">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F93">
         <v>1365</v>
@@ -8700,7 +8700,7 @@
         <v>14</v>
       </c>
       <c r="E94">
-        <v>0.49118125000000001</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F94">
         <v>1365</v>
@@ -8756,7 +8756,7 @@
         <v>14</v>
       </c>
       <c r="E95">
-        <v>0.52272499999999988</v>
+        <v>0.41817999999999989</v>
       </c>
       <c r="F95">
         <v>1365</v>
@@ -8812,7 +8812,7 @@
         <v>14</v>
       </c>
       <c r="E96">
-        <v>0.52272499999999988</v>
+        <v>0.41817999999999989</v>
       </c>
       <c r="F96">
         <v>1365</v>
@@ -8868,7 +8868,7 @@
         <v>14</v>
       </c>
       <c r="E97">
-        <v>0.52272499999999988</v>
+        <v>0.41817999999999989</v>
       </c>
       <c r="F97">
         <v>1365</v>
@@ -8924,7 +8924,7 @@
         <v>14</v>
       </c>
       <c r="E98">
-        <v>0.52272499999999988</v>
+        <v>0.41817999999999989</v>
       </c>
       <c r="F98">
         <v>1365</v>
@@ -8980,7 +8980,7 @@
         <v>14</v>
       </c>
       <c r="E99">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000011</v>
       </c>
       <c r="F99">
         <v>1365</v>
@@ -9036,7 +9036,7 @@
         <v>14</v>
       </c>
       <c r="E100">
-        <v>0.43259999999999998</v>
+        <v>0.34608000000000011</v>
       </c>
       <c r="F100">
         <v>1365</v>
@@ -9092,7 +9092,7 @@
         <v>14</v>
       </c>
       <c r="E101">
-        <v>0.49118125000000001</v>
+        <v>0.39294499999999999</v>
       </c>
       <c r="F101">
         <v>1365</v>
@@ -9148,7 +9148,7 @@
         <v>14</v>
       </c>
       <c r="E102">
-        <v>0.49118125000000001</v>
+        <v>0.39294499999999999</v>
       </c>
       <c r="F102">
         <v>1365</v>
@@ -9204,7 +9204,7 @@
         <v>14</v>
       </c>
       <c r="E103">
-        <v>0.49118125000000001</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F103">
         <v>1365</v>
@@ -9260,7 +9260,7 @@
         <v>14</v>
       </c>
       <c r="E104">
-        <v>0.52272499999999988</v>
+        <v>0.41818</v>
       </c>
       <c r="F104">
         <v>1365</v>
@@ -9316,7 +9316,7 @@
         <v>14</v>
       </c>
       <c r="E105">
-        <v>0.52272499999999988</v>
+        <v>0.41818</v>
       </c>
       <c r="F105">
         <v>1365</v>
@@ -9372,7 +9372,7 @@
         <v>14</v>
       </c>
       <c r="E106">
-        <v>0.52272499999999988</v>
+        <v>0.41818</v>
       </c>
       <c r="F106">
         <v>1365</v>
@@ -9428,7 +9428,7 @@
         <v>14</v>
       </c>
       <c r="E107">
-        <v>0.450625</v>
+        <v>0.36050000000000004</v>
       </c>
       <c r="F107">
         <v>1365</v>
@@ -9484,7 +9484,7 @@
         <v>14</v>
       </c>
       <c r="E108">
-        <v>0.450625</v>
+        <v>0.36050000000000004</v>
       </c>
       <c r="F108">
         <v>1365</v>
@@ -9540,7 +9540,7 @@
         <v>14</v>
       </c>
       <c r="E109">
-        <v>0.52272499999999988</v>
+        <v>0.41818</v>
       </c>
       <c r="F109">
         <v>1365</v>
@@ -9596,7 +9596,7 @@
         <v>14</v>
       </c>
       <c r="E110">
-        <v>0.52272499999999988</v>
+        <v>0.41817999999999989</v>
       </c>
       <c r="F110">
         <v>1365</v>
@@ -9652,7 +9652,7 @@
         <v>14</v>
       </c>
       <c r="E111">
-        <v>0.450625</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="F111">
         <v>1365</v>
@@ -9708,7 +9708,7 @@
         <v>14</v>
       </c>
       <c r="E112">
-        <v>0.50470000000000004</v>
+        <v>0.40376000000000006</v>
       </c>
       <c r="F112">
         <v>1365</v>
@@ -9764,7 +9764,7 @@
         <v>14</v>
       </c>
       <c r="E113">
-        <v>0.50470000000000004</v>
+        <v>0.40376000000000006</v>
       </c>
       <c r="F113">
         <v>1365</v>
@@ -9820,7 +9820,7 @@
         <v>14</v>
       </c>
       <c r="E114">
-        <v>0.48667500000000002</v>
+        <v>0.38934000000000002</v>
       </c>
       <c r="F114">
         <v>1365</v>
@@ -9876,7 +9876,7 @@
         <v>14</v>
       </c>
       <c r="E115">
-        <v>0.22981874999999999</v>
+        <v>0.18385499999999999</v>
       </c>
       <c r="F115">
         <v>1365</v>
@@ -9932,7 +9932,7 @@
         <v>14</v>
       </c>
       <c r="E116">
-        <v>0.2253125</v>
+        <v>0.18025000000000002</v>
       </c>
       <c r="F116">
         <v>1365</v>
@@ -9988,7 +9988,7 @@
         <v>14</v>
       </c>
       <c r="E117">
-        <v>0.27938750000000001</v>
+        <v>0.22351000000000007</v>
       </c>
       <c r="F117">
         <v>1365</v>
@@ -10044,7 +10044,7 @@
         <v>14</v>
       </c>
       <c r="E118">
-        <v>0.28839999999999999</v>
+        <v>0.23072000000000004</v>
       </c>
       <c r="F118">
         <v>1365</v>
@@ -10100,7 +10100,7 @@
         <v>14</v>
       </c>
       <c r="E119">
-        <v>0.16222500000000001</v>
+        <v>0.12978000000000001</v>
       </c>
       <c r="F119">
         <v>1365</v>
@@ -10156,7 +10156,7 @@
         <v>14</v>
       </c>
       <c r="E120">
-        <v>0.22981874999999999</v>
+        <v>0.18385499999999999</v>
       </c>
       <c r="F120">
         <v>1365</v>
@@ -10212,7 +10212,7 @@
         <v>14</v>
       </c>
       <c r="E121">
-        <v>0.22981874999999999</v>
+        <v>0.18385499999999999</v>
       </c>
       <c r="F121">
         <v>1365</v>
@@ -10268,7 +10268,7 @@
         <v>14</v>
       </c>
       <c r="E122">
-        <v>0.27037500000000003</v>
+        <v>0.21629999999999999</v>
       </c>
       <c r="F122">
         <v>1365</v>
@@ -10324,7 +10324,7 @@
         <v>14</v>
       </c>
       <c r="E123">
-        <v>0.27938750000000001</v>
+        <v>0.22351000000000007</v>
       </c>
       <c r="F123">
         <v>1365</v>
@@ -10380,7 +10380,7 @@
         <v>14</v>
       </c>
       <c r="E124">
-        <v>0.29741250000000002</v>
+        <v>0.23793000000000003</v>
       </c>
       <c r="F124">
         <v>1365</v>
@@ -10436,7 +10436,7 @@
         <v>14</v>
       </c>
       <c r="E125">
-        <v>0.24784375000000003</v>
+        <v>0.19827500000000003</v>
       </c>
       <c r="F125">
         <v>1365</v>
@@ -10492,7 +10492,7 @@
         <v>14</v>
       </c>
       <c r="E126">
-        <v>0.24784375000000003</v>
+        <v>0.19827500000000003</v>
       </c>
       <c r="F126">
         <v>1365</v>
@@ -10548,7 +10548,7 @@
         <v>14</v>
       </c>
       <c r="E127">
-        <v>0.26136249999999994</v>
+        <v>0.20909</v>
       </c>
       <c r="F127">
         <v>1365</v>
@@ -10604,7 +10604,7 @@
         <v>14</v>
       </c>
       <c r="E128">
-        <v>0.20728750000000001</v>
+        <v>0.16583000000000003</v>
       </c>
       <c r="F128">
         <v>1365</v>
@@ -10660,7 +10660,7 @@
         <v>14</v>
       </c>
       <c r="E129">
-        <v>0.22981874999999999</v>
+        <v>0.18385499999999999</v>
       </c>
       <c r="F129">
         <v>1365</v>
@@ -10716,7 +10716,7 @@
         <v>14</v>
       </c>
       <c r="E130">
-        <v>0.23883125000000002</v>
+        <v>0.19106500000000004</v>
       </c>
       <c r="F130">
         <v>1365</v>
@@ -10772,7 +10772,7 @@
         <v>14</v>
       </c>
       <c r="E131">
-        <v>0.29741250000000002</v>
+        <v>0.23793000000000003</v>
       </c>
       <c r="F131">
         <v>1365</v>
@@ -10828,7 +10828,7 @@
         <v>14</v>
       </c>
       <c r="E132">
-        <v>0.20728750000000001</v>
+        <v>0.16583000000000003</v>
       </c>
       <c r="F132">
         <v>1365</v>
@@ -10884,7 +10884,7 @@
         <v>14</v>
       </c>
       <c r="E133">
-        <v>0.20728750000000001</v>
+        <v>0.16583000000000003</v>
       </c>
       <c r="F133">
         <v>1365</v>
@@ -10940,7 +10940,7 @@
         <v>14</v>
       </c>
       <c r="E134">
-        <v>0.27938750000000001</v>
+        <v>0.22351000000000007</v>
       </c>
       <c r="F134">
         <v>1365</v>
@@ -10996,7 +10996,7 @@
         <v>14</v>
       </c>
       <c r="E135">
-        <v>0.32445000000000002</v>
+        <v>0.25956000000000001</v>
       </c>
       <c r="F135">
         <v>1365</v>
@@ -11052,7 +11052,7 @@
         <v>14</v>
       </c>
       <c r="E136">
-        <v>0.32445000000000002</v>
+        <v>0.25956000000000001</v>
       </c>
       <c r="F136">
         <v>1365</v>
@@ -11108,7 +11108,7 @@
         <v>14</v>
       </c>
       <c r="E137">
-        <v>0.32445000000000002</v>
+        <v>0.25956000000000001</v>
       </c>
       <c r="F137">
         <v>1365</v>
@@ -11164,7 +11164,7 @@
         <v>14</v>
       </c>
       <c r="E138">
-        <v>0.32445000000000002</v>
+        <v>0.25956000000000001</v>
       </c>
       <c r="F138">
         <v>1365</v>
@@ -11220,7 +11220,7 @@
         <v>14</v>
       </c>
       <c r="E139">
-        <v>0.32445000000000002</v>
+        <v>0.25956000000000001</v>
       </c>
       <c r="F139">
         <v>1365</v>
@@ -11276,7 +11276,7 @@
         <v>14</v>
       </c>
       <c r="E140">
-        <v>0.32445000000000002</v>
+        <v>0.25956000000000001</v>
       </c>
       <c r="F140">
         <v>1365</v>
@@ -11332,7 +11332,7 @@
         <v>14</v>
       </c>
       <c r="E141">
-        <v>0.32445000000000002</v>
+        <v>0.25956000000000001</v>
       </c>
       <c r="F141">
         <v>1365</v>
@@ -11388,7 +11388,7 @@
         <v>14</v>
       </c>
       <c r="E142">
-        <v>0.31093124999999999</v>
+        <v>0.24874500000000002</v>
       </c>
       <c r="F142">
         <v>1365</v>
@@ -11444,7 +11444,7 @@
         <v>14</v>
       </c>
       <c r="E143">
-        <v>0.30191875000000001</v>
+        <v>0.241535</v>
       </c>
       <c r="F143">
         <v>1365</v>
@@ -11836,7 +11836,7 @@
         <v>14</v>
       </c>
       <c r="E150">
-        <v>0.19827500000000001</v>
+        <v>0.15862000000000001</v>
       </c>
       <c r="F150">
         <v>1365</v>
@@ -11892,7 +11892,7 @@
         <v>14</v>
       </c>
       <c r="E151">
-        <v>0.21629999999999999</v>
+        <v>0.17304000000000003</v>
       </c>
       <c r="F151">
         <v>1365</v>
@@ -11948,7 +11948,7 @@
         <v>14</v>
       </c>
       <c r="E152">
-        <v>0.26136249999999994</v>
+        <v>0.20909</v>
       </c>
       <c r="F152">
         <v>1365</v>
@@ -12004,7 +12004,7 @@
         <v>14</v>
       </c>
       <c r="E153">
-        <v>0.18025000000000002</v>
+        <v>0.14420000000000002</v>
       </c>
       <c r="F153">
         <v>1365</v>
@@ -12060,7 +12060,7 @@
         <v>14</v>
       </c>
       <c r="E154">
-        <v>0.1892625</v>
+        <v>0.15140999999999999</v>
       </c>
       <c r="F154">
         <v>1365</v>
@@ -12116,7 +12116,7 @@
         <v>14</v>
       </c>
       <c r="E155">
-        <v>0.28389375</v>
+        <v>0.22711500000000001</v>
       </c>
       <c r="F155">
         <v>1365</v>
@@ -12172,7 +12172,7 @@
         <v>14</v>
       </c>
       <c r="E156">
-        <v>0.28389375</v>
+        <v>0.22711500000000001</v>
       </c>
       <c r="F156">
         <v>1365</v>
@@ -12228,7 +12228,7 @@
         <v>14</v>
       </c>
       <c r="E157">
-        <v>0.25685625000000001</v>
+        <v>0.205485</v>
       </c>
       <c r="F157">
         <v>1365</v>
@@ -12302,7 +12302,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{264D6273-DCDE-48A2-9F0E-304D2624E41C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C9561B5-05D1-4382-8A2F-EA45D110B6BF}">
   <dimension ref="B9:T213"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23369,7 +23369,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C38526E8-6F9E-4DA1-B69D-66D73299D519}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60214CCD-DFE3-425E-83E3-FCA22AD584A7}">
   <dimension ref="B9:T683"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23454,7 +23454,7 @@
         <v>0.03</v>
       </c>
       <c r="G11">
-        <v>0.18540000000000001</v>
+        <v>0.14832000000000001</v>
       </c>
       <c r="H11">
         <v>5197.5</v>
@@ -23507,7 +23507,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="G12">
-        <v>0.26264999999999999</v>
+        <v>0.21012</v>
       </c>
       <c r="H12">
         <v>5197.5</v>
@@ -23560,7 +23560,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="G13">
-        <v>0.26264999999999999</v>
+        <v>0.21011999999999997</v>
       </c>
       <c r="H13">
         <v>5197.5</v>
@@ -23613,7 +23613,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="G14">
-        <v>0.26264999999999999</v>
+        <v>0.21012</v>
       </c>
       <c r="H14">
         <v>5197.5</v>
@@ -23666,7 +23666,7 @@
         <v>0.03</v>
       </c>
       <c r="G15">
-        <v>0.28840000000000005</v>
+        <v>0.23072000000000006</v>
       </c>
       <c r="H15">
         <v>5197.5</v>
@@ -23719,7 +23719,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
       <c r="G16">
-        <v>0.28840000000000005</v>
+        <v>0.23072000000000004</v>
       </c>
       <c r="H16">
         <v>5197.5</v>
@@ -23772,7 +23772,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="G17">
-        <v>0.28840000000000005</v>
+        <v>0.23072000000000006</v>
       </c>
       <c r="H17">
         <v>5197.5</v>
@@ -23825,7 +23825,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="G18">
-        <v>0.309</v>
+        <v>0.2472</v>
       </c>
       <c r="H18">
         <v>5197.5</v>
@@ -23878,7 +23878,7 @@
         <v>0.11799999999999999</v>
       </c>
       <c r="G19">
-        <v>0.30899999999999994</v>
+        <v>0.2472</v>
       </c>
       <c r="H19">
         <v>5197.5</v>
@@ -23931,7 +23931,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G20">
-        <v>0.309</v>
+        <v>0.24720000000000003</v>
       </c>
       <c r="H20">
         <v>5197.5</v>
@@ -23984,7 +23984,7 @@
         <v>7.8E-2</v>
       </c>
       <c r="G21">
-        <v>0.30899999999999994</v>
+        <v>0.24719999999999998</v>
       </c>
       <c r="H21">
         <v>5197.5</v>
@@ -24037,7 +24037,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="G22">
-        <v>0.309</v>
+        <v>0.2472</v>
       </c>
       <c r="H22">
         <v>5197.5</v>
@@ -24090,7 +24090,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="G23">
-        <v>0.309</v>
+        <v>0.2472</v>
       </c>
       <c r="H23">
         <v>5197.5</v>
@@ -24143,7 +24143,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G24">
-        <v>0.309</v>
+        <v>0.24720000000000003</v>
       </c>
       <c r="H24">
         <v>5197.5</v>
@@ -24196,7 +24196,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="G25">
-        <v>0.3296</v>
+        <v>0.26368000000000003</v>
       </c>
       <c r="H25">
         <v>5197.5</v>
@@ -24249,7 +24249,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="G26">
-        <v>0.3296</v>
+        <v>0.26368000000000003</v>
       </c>
       <c r="H26">
         <v>5197.5</v>
@@ -24302,7 +24302,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="G27">
-        <v>0.3296</v>
+        <v>0.26368000000000003</v>
       </c>
       <c r="H27">
         <v>5197.5</v>
@@ -24355,7 +24355,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="G28">
-        <v>0.3296</v>
+        <v>0.26368000000000003</v>
       </c>
       <c r="H28">
         <v>5197.5</v>
@@ -24408,7 +24408,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
       <c r="G29">
-        <v>0.3296</v>
+        <v>0.26368000000000003</v>
       </c>
       <c r="H29">
         <v>5197.5</v>
@@ -24461,7 +24461,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G30">
-        <v>0.33990000000000004</v>
+        <v>0.27192000000000005</v>
       </c>
       <c r="H30">
         <v>4427.5</v>
@@ -24514,7 +24514,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
       <c r="G31">
-        <v>0.31930000000000003</v>
+        <v>0.25544000000000006</v>
       </c>
       <c r="H31">
         <v>4427.5</v>
@@ -24567,7 +24567,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G32">
-        <v>0.31930000000000003</v>
+        <v>0.25544000000000006</v>
       </c>
       <c r="H32">
         <v>4427.5</v>
@@ -24620,7 +24620,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G33">
-        <v>0.33990000000000004</v>
+        <v>0.27192000000000005</v>
       </c>
       <c r="H33">
         <v>4427.5</v>
@@ -24673,7 +24673,7 @@
         <v>5.5E-2</v>
       </c>
       <c r="G34">
-        <v>0.31930000000000003</v>
+        <v>0.25544000000000006</v>
       </c>
       <c r="H34">
         <v>4427.5</v>
@@ -24726,7 +24726,7 @@
         <v>6.2E-2</v>
       </c>
       <c r="G35">
-        <v>0.31930000000000003</v>
+        <v>0.25544000000000006</v>
       </c>
       <c r="H35">
         <v>4427.5</v>
@@ -24779,7 +24779,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="G36">
-        <v>0.33990000000000004</v>
+        <v>0.27192000000000005</v>
       </c>
       <c r="H36">
         <v>4427.5</v>
@@ -24832,7 +24832,7 @@
         <v>0.06</v>
       </c>
       <c r="G37">
-        <v>0.33990000000000004</v>
+        <v>0.27192000000000005</v>
       </c>
       <c r="H37">
         <v>4427.5</v>
@@ -24885,7 +24885,7 @@
         <v>0.05</v>
       </c>
       <c r="G38">
-        <v>0.3296</v>
+        <v>0.26368000000000003</v>
       </c>
       <c r="H38">
         <v>5197.5</v>
@@ -24938,7 +24938,7 @@
         <v>0.05</v>
       </c>
       <c r="G39">
-        <v>0.3296</v>
+        <v>0.26368000000000003</v>
       </c>
       <c r="H39">
         <v>5197.5</v>
@@ -24991,7 +24991,7 @@
         <v>0.29899999999999999</v>
       </c>
       <c r="G40">
-        <v>0.33990000000000004</v>
+        <v>0.27192000000000005</v>
       </c>
       <c r="H40">
         <v>4427.5</v>
@@ -25044,7 +25044,7 @@
         <v>0.05</v>
       </c>
       <c r="G41">
-        <v>0.309</v>
+        <v>0.24719999999999998</v>
       </c>
       <c r="H41">
         <v>5197.5</v>
@@ -25097,7 +25097,7 @@
         <v>0.64500000000000002</v>
       </c>
       <c r="G42">
-        <v>0.27810000000000001</v>
+        <v>0.22248000000000001</v>
       </c>
       <c r="H42">
         <v>3850.0000000000009</v>
@@ -25150,7 +25150,7 @@
         <v>0.64500000000000002</v>
       </c>
       <c r="G43">
-        <v>0.27810000000000001</v>
+        <v>0.22248000000000001</v>
       </c>
       <c r="H43">
         <v>3850.0000000000009</v>
@@ -25203,7 +25203,7 @@
         <v>0.64500000000000002</v>
       </c>
       <c r="G44">
-        <v>0.27810000000000001</v>
+        <v>0.22248000000000001</v>
       </c>
       <c r="H44">
         <v>3850.0000000000009</v>
@@ -25256,7 +25256,7 @@
         <v>0.64500000000000002</v>
       </c>
       <c r="G45">
-        <v>0.28325000000000006</v>
+        <v>0.22660000000000005</v>
       </c>
       <c r="H45">
         <v>3850.0000000000009</v>
@@ -25309,7 +25309,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G46">
-        <v>0.31930000000000003</v>
+        <v>0.25544000000000006</v>
       </c>
       <c r="H46">
         <v>4427.5</v>
@@ -25362,7 +25362,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G47">
-        <v>0.25750000000000001</v>
+        <v>0.20600000000000002</v>
       </c>
       <c r="H47">
         <v>4427.5</v>
@@ -25415,7 +25415,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G48">
-        <v>0.25750000000000001</v>
+        <v>0.20600000000000002</v>
       </c>
       <c r="H48">
         <v>4427.5</v>
@@ -25468,7 +25468,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="G49">
-        <v>0.33990000000000004</v>
+        <v>0.27192000000000005</v>
       </c>
       <c r="H49">
         <v>4427.5</v>
@@ -25521,7 +25521,7 @@
         <v>2.4270000000000005</v>
       </c>
       <c r="G50">
-        <v>0.36049999999999999</v>
+        <v>0.28839999999999999</v>
       </c>
       <c r="H50">
         <v>3850.0000000000009</v>
@@ -25574,7 +25574,7 @@
         <v>5.23</v>
       </c>
       <c r="G51">
-        <v>0.33123000000000002</v>
+        <v>0.26498400000000005</v>
       </c>
       <c r="N51" t="s">
         <v>334</v>
@@ -25615,7 +25615,7 @@
         <v>2.3E-2</v>
       </c>
       <c r="G52">
-        <v>0.51500000000000001</v>
+        <v>0.41200000000000003</v>
       </c>
       <c r="H52">
         <v>1485.0000000000002</v>
@@ -25668,7 +25668,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G53">
-        <v>0.55620000000000003</v>
+        <v>0.44496000000000008</v>
       </c>
       <c r="H53">
         <v>1485.0000000000002</v>
@@ -25721,7 +25721,7 @@
         <v>0.3</v>
       </c>
       <c r="G54">
-        <v>0.53560000000000008</v>
+        <v>0.42848000000000003</v>
       </c>
       <c r="H54">
         <v>1265</v>
@@ -25774,7 +25774,7 @@
         <v>0.3</v>
       </c>
       <c r="G55">
-        <v>0.53560000000000008</v>
+        <v>0.42848000000000003</v>
       </c>
       <c r="H55">
         <v>1265</v>
@@ -25827,7 +25827,7 @@
         <v>0.06</v>
       </c>
       <c r="G56">
-        <v>0.53560000000000008</v>
+        <v>0.42848000000000008</v>
       </c>
       <c r="H56">
         <v>1265</v>
@@ -25880,7 +25880,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="G57">
-        <v>0.51500000000000001</v>
+        <v>0.41200000000000003</v>
       </c>
       <c r="H57">
         <v>1265</v>
@@ -25933,7 +25933,7 @@
         <v>0.45500000000000002</v>
       </c>
       <c r="G58">
-        <v>0.59739999999999993</v>
+        <v>0.4779199999999999</v>
       </c>
       <c r="H58">
         <v>1100</v>
@@ -25986,7 +25986,7 @@
         <v>0.375</v>
       </c>
       <c r="G59">
-        <v>0.54075000000000006</v>
+        <v>0.43260000000000004</v>
       </c>
       <c r="H59">
         <v>1100</v>
@@ -26039,7 +26039,7 @@
         <v>0.375</v>
       </c>
       <c r="G60">
-        <v>0.54075000000000006</v>
+        <v>0.43260000000000004</v>
       </c>
       <c r="H60">
         <v>1100</v>
@@ -26092,7 +26092,7 @@
         <v>0.375</v>
       </c>
       <c r="G61">
-        <v>0.54075000000000006</v>
+        <v>0.43260000000000004</v>
       </c>
       <c r="H61">
         <v>1100</v>
@@ -26145,7 +26145,7 @@
         <v>0.375</v>
       </c>
       <c r="G62">
-        <v>0.54075000000000006</v>
+        <v>0.43260000000000004</v>
       </c>
       <c r="H62">
         <v>1100</v>
@@ -26198,7 +26198,7 @@
         <v>0.41299999999999998</v>
       </c>
       <c r="G63">
-        <v>0.56135000000000002</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H63">
         <v>1100</v>
@@ -26251,7 +26251,7 @@
         <v>0.40699999999999997</v>
       </c>
       <c r="G64">
-        <v>0.54075000000000006</v>
+        <v>0.4326000000000001</v>
       </c>
       <c r="H64">
         <v>1100</v>
@@ -26304,7 +26304,7 @@
         <v>0.8</v>
       </c>
       <c r="G65">
-        <v>0.56135000000000002</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H65">
         <v>1100</v>
@@ -26357,7 +26357,7 @@
         <v>0.44500000000000001</v>
       </c>
       <c r="G66">
-        <v>0.54075000000000006</v>
+        <v>0.4326000000000001</v>
       </c>
       <c r="H66">
         <v>1100</v>
@@ -26410,7 +26410,7 @@
         <v>0.80500000000000005</v>
       </c>
       <c r="G67">
-        <v>0.54075000000000006</v>
+        <v>0.43260000000000004</v>
       </c>
       <c r="H67">
         <v>1100</v>
@@ -26463,7 +26463,7 @@
         <v>0.78</v>
       </c>
       <c r="G68">
-        <v>0.54075000000000006</v>
+        <v>0.4326000000000001</v>
       </c>
       <c r="H68">
         <v>1100</v>
@@ -26516,7 +26516,7 @@
         <v>0.71</v>
       </c>
       <c r="G69">
-        <v>0.54075000000000006</v>
+        <v>0.4326000000000001</v>
       </c>
       <c r="H69">
         <v>1100</v>
@@ -26569,7 +26569,7 @@
         <v>0.40799999999999997</v>
       </c>
       <c r="G70">
-        <v>0.54075000000000006</v>
+        <v>0.43260000000000004</v>
       </c>
       <c r="H70">
         <v>1100</v>
@@ -26622,7 +26622,7 @@
         <v>0.155</v>
       </c>
       <c r="G71">
-        <v>0.51500000000000001</v>
+        <v>0.41200000000000003</v>
       </c>
       <c r="H71">
         <v>1265</v>
@@ -26675,7 +26675,7 @@
         <v>0.45500000000000002</v>
       </c>
       <c r="G72">
-        <v>0.59739999999999993</v>
+        <v>0.4779199999999999</v>
       </c>
       <c r="H72">
         <v>1100</v>
@@ -26728,7 +26728,7 @@
         <v>0.45500000000000002</v>
       </c>
       <c r="G73">
-        <v>0.59739999999999993</v>
+        <v>0.4779199999999999</v>
       </c>
       <c r="H73">
         <v>1100</v>
@@ -26781,7 +26781,7 @@
         <v>0.45500000000000002</v>
       </c>
       <c r="G74">
-        <v>0.59739999999999993</v>
+        <v>0.4779199999999999</v>
       </c>
       <c r="H74">
         <v>1100</v>
@@ -26834,7 +26834,7 @@
         <v>0.14499999999999999</v>
       </c>
       <c r="G75">
-        <v>0.53560000000000008</v>
+        <v>0.42848000000000008</v>
       </c>
       <c r="H75">
         <v>1265</v>
@@ -26887,7 +26887,7 @@
         <v>0.39800000000000002</v>
       </c>
       <c r="G76">
-        <v>0.56135000000000002</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H76">
         <v>1100</v>
@@ -26940,7 +26940,7 @@
         <v>0.76400000000000001</v>
       </c>
       <c r="G77">
-        <v>0.54075000000000006</v>
+        <v>0.43260000000000015</v>
       </c>
       <c r="H77">
         <v>1100</v>
@@ -26993,7 +26993,7 @@
         <v>0.89300000000000002</v>
       </c>
       <c r="G78">
-        <v>0.61799999999999999</v>
+        <v>0.49440000000000006</v>
       </c>
       <c r="H78">
         <v>1100</v>
@@ -27046,7 +27046,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="G79">
-        <v>0.59739999999999993</v>
+        <v>0.47791999999999996</v>
       </c>
       <c r="H79">
         <v>1265</v>
@@ -27099,7 +27099,7 @@
         <v>0.90500000000000003</v>
       </c>
       <c r="G80">
-        <v>0.56135000000000002</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H80">
         <v>1100</v>
@@ -27152,7 +27152,7 @@
         <v>0.73499999999999999</v>
       </c>
       <c r="G81">
-        <v>0.54075000000000006</v>
+        <v>0.4326000000000001</v>
       </c>
       <c r="H81">
         <v>1100</v>
@@ -27205,7 +27205,7 @@
         <v>0.92</v>
       </c>
       <c r="G82">
-        <v>0.56135000000000002</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H82">
         <v>1100</v>
@@ -27258,7 +27258,7 @@
         <v>0.755</v>
       </c>
       <c r="G83">
-        <v>0.54075000000000006</v>
+        <v>0.4326000000000001</v>
       </c>
       <c r="H83">
         <v>1100</v>
@@ -27311,7 +27311,7 @@
         <v>0.46500000000000002</v>
       </c>
       <c r="G84">
-        <v>0.59739999999999982</v>
+        <v>0.47791999999999996</v>
       </c>
       <c r="H84">
         <v>1100</v>
@@ -27364,7 +27364,7 @@
         <v>0.46500000000000002</v>
       </c>
       <c r="G85">
-        <v>0.59739999999999982</v>
+        <v>0.47791999999999996</v>
       </c>
       <c r="H85">
         <v>1100</v>
@@ -27417,7 +27417,7 @@
         <v>0.46500000000000002</v>
       </c>
       <c r="G86">
-        <v>0.59739999999999982</v>
+        <v>0.47791999999999996</v>
       </c>
       <c r="H86">
         <v>1100</v>
@@ -27470,7 +27470,7 @@
         <v>0.44500000000000001</v>
       </c>
       <c r="G87">
-        <v>0.59739999999999993</v>
+        <v>0.47791999999999996</v>
       </c>
       <c r="H87">
         <v>1100</v>
@@ -27523,7 +27523,7 @@
         <v>0.46500000000000002</v>
       </c>
       <c r="G88">
-        <v>0.59739999999999982</v>
+        <v>0.47791999999999996</v>
       </c>
       <c r="H88">
         <v>1100</v>
@@ -27576,7 +27576,7 @@
         <v>0.245</v>
       </c>
       <c r="G89">
-        <v>0.51500000000000001</v>
+        <v>0.41200000000000003</v>
       </c>
       <c r="H89">
         <v>1265</v>
@@ -27629,7 +27629,7 @@
         <v>1.18</v>
       </c>
       <c r="G90">
-        <v>0.54075000000000006</v>
+        <v>0.4326000000000001</v>
       </c>
       <c r="H90">
         <v>1100</v>
@@ -27682,7 +27682,7 @@
         <v>0.81</v>
       </c>
       <c r="G91">
-        <v>0.54075000000000006</v>
+        <v>0.4326000000000001</v>
       </c>
       <c r="H91">
         <v>1100</v>
@@ -27735,7 +27735,7 @@
         <v>0.71499999999999997</v>
       </c>
       <c r="G92">
-        <v>0.54075000000000006</v>
+        <v>0.4326000000000001</v>
       </c>
       <c r="H92">
         <v>1100</v>
@@ -27788,7 +27788,7 @@
         <v>0.4</v>
       </c>
       <c r="G93">
-        <v>0.54075000000000006</v>
+        <v>0.4326000000000001</v>
       </c>
       <c r="H93">
         <v>1100</v>
@@ -27841,7 +27841,7 @@
         <v>0.4</v>
       </c>
       <c r="G94">
-        <v>0.54075000000000006</v>
+        <v>0.4326000000000001</v>
       </c>
       <c r="H94">
         <v>1100</v>
@@ -27894,7 +27894,7 @@
         <v>0.4</v>
       </c>
       <c r="G95">
-        <v>0.54075000000000006</v>
+        <v>0.4326000000000001</v>
       </c>
       <c r="H95">
         <v>1100</v>
@@ -27947,7 +27947,7 @@
         <v>0.83599999999999997</v>
       </c>
       <c r="G96">
-        <v>0.54075000000000006</v>
+        <v>0.4326000000000001</v>
       </c>
       <c r="H96">
         <v>1100</v>
@@ -28000,7 +28000,7 @@
         <v>0.42199999999999999</v>
       </c>
       <c r="G97">
-        <v>0.54075000000000006</v>
+        <v>0.4326000000000001</v>
       </c>
       <c r="H97">
         <v>1100</v>
@@ -28053,7 +28053,7 @@
         <v>0.42499999999999999</v>
       </c>
       <c r="G98">
-        <v>0.56135000000000002</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H98">
         <v>1100</v>
@@ -28106,7 +28106,7 @@
         <v>0.42499999999999999</v>
       </c>
       <c r="G99">
-        <v>0.59739999999999993</v>
+        <v>0.47791999999999996</v>
       </c>
       <c r="H99">
         <v>1100</v>
@@ -28159,7 +28159,7 @@
         <v>0.42</v>
       </c>
       <c r="G100">
-        <v>0.54075000000000006</v>
+        <v>0.4326000000000001</v>
       </c>
       <c r="H100">
         <v>1100</v>
@@ -28212,7 +28212,7 @@
         <v>0.81</v>
       </c>
       <c r="G101">
-        <v>0.54075000000000006</v>
+        <v>0.4326000000000001</v>
       </c>
       <c r="H101">
         <v>1100</v>
@@ -28265,7 +28265,7 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="G102">
-        <v>0.54075000000000006</v>
+        <v>0.4326000000000001</v>
       </c>
       <c r="H102">
         <v>1100</v>
@@ -28318,7 +28318,7 @@
         <v>0.65</v>
       </c>
       <c r="G103">
-        <v>0.56135000000000002</v>
+        <v>0.44908000000000009</v>
       </c>
       <c r="H103">
         <v>1100</v>
@@ -28371,7 +28371,7 @@
         <v>0.443</v>
       </c>
       <c r="G104">
-        <v>0.59739999999999993</v>
+        <v>0.4779199999999999</v>
       </c>
       <c r="H104">
         <v>1100</v>
@@ -28424,7 +28424,7 @@
         <v>0.443</v>
       </c>
       <c r="G105">
-        <v>0.59739999999999993</v>
+        <v>0.4779199999999999</v>
       </c>
       <c r="H105">
         <v>1100</v>
@@ -28477,7 +28477,7 @@
         <v>0.443</v>
       </c>
       <c r="G106">
-        <v>0.59739999999999993</v>
+        <v>0.4779199999999999</v>
       </c>
       <c r="H106">
         <v>1100</v>
@@ -28530,7 +28530,7 @@
         <v>0.443</v>
       </c>
       <c r="G107">
-        <v>0.59739999999999993</v>
+        <v>0.4779199999999999</v>
       </c>
       <c r="H107">
         <v>1100</v>
@@ -28583,7 +28583,7 @@
         <v>0.81899999999999995</v>
       </c>
       <c r="G108">
-        <v>0.54075000000000006</v>
+        <v>0.43260000000000015</v>
       </c>
       <c r="H108">
         <v>1100</v>
@@ -28636,7 +28636,7 @@
         <v>0.05</v>
       </c>
       <c r="G109">
-        <v>0.49439999999999995</v>
+        <v>0.39552000000000009</v>
       </c>
       <c r="H109">
         <v>1485.0000000000002</v>
@@ -28689,7 +28689,7 @@
         <v>0.375</v>
       </c>
       <c r="G110">
-        <v>0.56135000000000002</v>
+        <v>0.44907999999999998</v>
       </c>
       <c r="H110">
         <v>1100</v>
@@ -28742,7 +28742,7 @@
         <v>0.375</v>
       </c>
       <c r="G111">
-        <v>0.56135000000000002</v>
+        <v>0.44907999999999998</v>
       </c>
       <c r="H111">
         <v>1100</v>
@@ -28795,7 +28795,7 @@
         <v>0.53</v>
       </c>
       <c r="G112">
-        <v>0.56135000000000002</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H112">
         <v>1100</v>
@@ -28848,7 +28848,7 @@
         <v>0.45</v>
       </c>
       <c r="G113">
-        <v>0.59739999999999993</v>
+        <v>0.47792000000000001</v>
       </c>
       <c r="H113">
         <v>1100</v>
@@ -28901,7 +28901,7 @@
         <v>0.46</v>
       </c>
       <c r="G114">
-        <v>0.59739999999999993</v>
+        <v>0.47791999999999996</v>
       </c>
       <c r="H114">
         <v>1100</v>
@@ -28954,7 +28954,7 @@
         <v>0.45</v>
       </c>
       <c r="G115">
-        <v>0.59739999999999993</v>
+        <v>0.47792000000000001</v>
       </c>
       <c r="H115">
         <v>1100</v>
@@ -29007,7 +29007,7 @@
         <v>9.4E-2</v>
       </c>
       <c r="G116">
-        <v>0.51500000000000001</v>
+        <v>0.41200000000000003</v>
       </c>
       <c r="H116">
         <v>1265</v>
@@ -29060,7 +29060,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="G117">
-        <v>0.51500000000000001</v>
+        <v>0.41200000000000003</v>
       </c>
       <c r="H117">
         <v>1265</v>
@@ -29113,7 +29113,7 @@
         <v>0.39500000000000002</v>
       </c>
       <c r="G118">
-        <v>0.59739999999999993</v>
+        <v>0.47791999999999996</v>
       </c>
       <c r="H118">
         <v>1100</v>
@@ -29166,7 +29166,7 @@
         <v>0.45500000000000002</v>
       </c>
       <c r="G119">
-        <v>0.59739999999999993</v>
+        <v>0.4779199999999999</v>
       </c>
       <c r="H119">
         <v>1100</v>
@@ -29219,7 +29219,7 @@
         <v>5.5E-2</v>
       </c>
       <c r="G120">
-        <v>0.51500000000000001</v>
+        <v>0.41199999999999998</v>
       </c>
       <c r="H120">
         <v>1265</v>
@@ -29272,7 +29272,7 @@
         <v>0.115</v>
       </c>
       <c r="G121">
-        <v>0.57680000000000009</v>
+        <v>0.46144000000000007</v>
       </c>
       <c r="H121">
         <v>1265</v>
@@ -29325,7 +29325,7 @@
         <v>0.13500000000000001</v>
       </c>
       <c r="G122">
-        <v>0.57680000000000009</v>
+        <v>0.46144000000000007</v>
       </c>
       <c r="H122">
         <v>1265</v>
@@ -29378,7 +29378,7 @@
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="G123">
-        <v>0.2266</v>
+        <v>0.18128</v>
       </c>
       <c r="H123">
         <v>1188</v>
@@ -29431,7 +29431,7 @@
         <v>0.03</v>
       </c>
       <c r="G124">
-        <v>0.26264999999999999</v>
+        <v>0.21012</v>
       </c>
       <c r="H124">
         <v>1188</v>
@@ -29484,7 +29484,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="G125">
-        <v>0.26264999999999999</v>
+        <v>0.21012</v>
       </c>
       <c r="H125">
         <v>1188</v>
@@ -29505,7 +29505,7 @@
         <v>129</v>
       </c>
       <c r="P125" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q125" t="s">
         <v>336</v>
@@ -29537,7 +29537,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G126">
-        <v>0.26264999999999999</v>
+        <v>0.21012000000000003</v>
       </c>
       <c r="H126">
         <v>1188</v>
@@ -29558,7 +29558,7 @@
         <v>129</v>
       </c>
       <c r="P126" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q126" t="s">
         <v>336</v>
@@ -29590,7 +29590,7 @@
         <v>0.04</v>
       </c>
       <c r="G127">
-        <v>0.26264999999999999</v>
+        <v>0.21012</v>
       </c>
       <c r="H127">
         <v>1188</v>
@@ -29643,7 +29643,7 @@
         <v>0.03</v>
       </c>
       <c r="G128">
-        <v>0.28840000000000005</v>
+        <v>0.23072000000000006</v>
       </c>
       <c r="H128">
         <v>1188</v>
@@ -29696,7 +29696,7 @@
         <v>0.14399999999999999</v>
       </c>
       <c r="G129">
-        <v>0.28839999999999999</v>
+        <v>0.23072000000000006</v>
       </c>
       <c r="H129">
         <v>1188</v>
@@ -29749,7 +29749,7 @@
         <v>0.02</v>
       </c>
       <c r="G130">
-        <v>0.309</v>
+        <v>0.2472</v>
       </c>
       <c r="H130">
         <v>1188</v>
@@ -29802,7 +29802,7 @@
         <v>0.04</v>
       </c>
       <c r="G131">
-        <v>0.309</v>
+        <v>0.2472</v>
       </c>
       <c r="H131">
         <v>1188</v>
@@ -29855,7 +29855,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G132">
-        <v>0.31930000000000003</v>
+        <v>0.25544000000000006</v>
       </c>
       <c r="H132">
         <v>1188</v>
@@ -29908,7 +29908,7 @@
         <v>0.05</v>
       </c>
       <c r="G133">
-        <v>0.26264999999999999</v>
+        <v>0.21012</v>
       </c>
       <c r="H133">
         <v>1188</v>
@@ -29961,7 +29961,7 @@
         <v>0.125</v>
       </c>
       <c r="G134">
-        <v>0.25750000000000001</v>
+        <v>0.20600000000000002</v>
       </c>
       <c r="H134">
         <v>1012</v>
@@ -30014,7 +30014,7 @@
         <v>0.3</v>
       </c>
       <c r="G135">
-        <v>0.31930000000000003</v>
+        <v>0.25544000000000006</v>
       </c>
       <c r="H135">
         <v>1012</v>
@@ -30067,7 +30067,7 @@
         <v>0.29899999999999999</v>
       </c>
       <c r="G136">
-        <v>0.3296</v>
+        <v>0.26368000000000003</v>
       </c>
       <c r="H136">
         <v>1012</v>
@@ -30120,7 +30120,7 @@
         <v>0.05</v>
       </c>
       <c r="G137">
-        <v>0.18539999999999998</v>
+        <v>0.14832000000000001</v>
       </c>
       <c r="H137">
         <v>1188</v>
@@ -30173,7 +30173,7 @@
         <v>0.05</v>
       </c>
       <c r="G138">
-        <v>0.26264999999999999</v>
+        <v>0.21012</v>
       </c>
       <c r="H138">
         <v>1188</v>
@@ -30226,7 +30226,7 @@
         <v>0.05</v>
       </c>
       <c r="G139">
-        <v>0.26264999999999999</v>
+        <v>0.21012</v>
       </c>
       <c r="H139">
         <v>1188</v>
@@ -30279,7 +30279,7 @@
         <v>0.05</v>
       </c>
       <c r="G140">
-        <v>0.309</v>
+        <v>0.24719999999999998</v>
       </c>
       <c r="H140">
         <v>1188</v>
@@ -30332,7 +30332,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
       <c r="G141">
-        <v>0.31930000000000003</v>
+        <v>0.25544000000000006</v>
       </c>
       <c r="H141">
         <v>1012</v>
@@ -30385,7 +30385,7 @@
         <v>0.34</v>
       </c>
       <c r="G142">
-        <v>0.33990000000000004</v>
+        <v>0.27192000000000005</v>
       </c>
       <c r="H142">
         <v>880.00000000000023</v>
@@ -30438,7 +30438,7 @@
         <v>0.311</v>
       </c>
       <c r="G143">
-        <v>0.28325000000000006</v>
+        <v>0.22660000000000005</v>
       </c>
       <c r="H143">
         <v>880.00000000000023</v>
@@ -30491,7 +30491,7 @@
         <v>0.311</v>
       </c>
       <c r="G144">
-        <v>0.28325000000000006</v>
+        <v>0.22660000000000005</v>
       </c>
       <c r="H144">
         <v>880.00000000000023</v>
@@ -30544,7 +30544,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
       <c r="G145">
-        <v>0.29869999999999997</v>
+        <v>0.23895999999999998</v>
       </c>
       <c r="H145">
         <v>1012</v>
@@ -30597,7 +30597,7 @@
         <v>0.06</v>
       </c>
       <c r="G146">
-        <v>0.23690000000000003</v>
+        <v>0.18952000000000002</v>
       </c>
       <c r="H146">
         <v>1012</v>
@@ -30650,7 +30650,7 @@
         <v>0.05</v>
       </c>
       <c r="G147">
-        <v>0.26264999999999999</v>
+        <v>0.21012</v>
       </c>
       <c r="H147">
         <v>1188</v>
@@ -30703,7 +30703,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G148">
-        <v>0.27295000000000003</v>
+        <v>0.21836000000000003</v>
       </c>
       <c r="H148">
         <v>1012</v>
@@ -30756,7 +30756,7 @@
         <v>0.34</v>
       </c>
       <c r="G149">
-        <v>0.33990000000000004</v>
+        <v>0.27192000000000005</v>
       </c>
       <c r="H149">
         <v>880.00000000000023</v>
@@ -30809,7 +30809,7 @@
         <v>0.06</v>
       </c>
       <c r="G150">
-        <v>0.23690000000000003</v>
+        <v>0.18952000000000002</v>
       </c>
       <c r="H150">
         <v>1012</v>
@@ -30862,7 +30862,7 @@
         <v>0.1</v>
       </c>
       <c r="G151">
-        <v>0.2369</v>
+        <v>0.18952000000000002</v>
       </c>
       <c r="H151">
         <v>1012</v>
@@ -30915,7 +30915,7 @@
         <v>0.14199999999999999</v>
       </c>
       <c r="G152">
-        <v>0.36564999999999998</v>
+        <v>0.29252</v>
       </c>
       <c r="H152">
         <v>1633.5000000000002</v>
@@ -30968,7 +30968,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="G153">
-        <v>0.36564999999999998</v>
+        <v>0.29252</v>
       </c>
       <c r="H153">
         <v>1633.5000000000005</v>
@@ -31021,7 +31021,7 @@
         <v>4.9500000000000002E-2</v>
       </c>
       <c r="G154">
-        <v>0.36564999999999998</v>
+        <v>0.29252</v>
       </c>
       <c r="H154">
         <v>1633.5000000000002</v>
@@ -31074,7 +31074,7 @@
         <v>8.6400000000000005E-2</v>
       </c>
       <c r="G155">
-        <v>0.36564999999999998</v>
+        <v>0.29252</v>
       </c>
       <c r="H155">
         <v>1633.5000000000002</v>
@@ -31127,7 +31127,7 @@
         <v>2.0500000000000001E-2</v>
       </c>
       <c r="G156">
-        <v>0.36564999999999998</v>
+        <v>0.29252</v>
       </c>
       <c r="H156">
         <v>1633.5000000000005</v>
@@ -31180,7 +31180,7 @@
         <v>0.1295</v>
       </c>
       <c r="G157">
-        <v>0.36564999999999998</v>
+        <v>0.29252</v>
       </c>
       <c r="H157">
         <v>1633.5000000000005</v>
@@ -31233,7 +31233,7 @@
         <v>8.1700000000000009E-2</v>
       </c>
       <c r="G158">
-        <v>0.37080000000000002</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H158">
         <v>1633.5</v>
@@ -31286,7 +31286,7 @@
         <v>0.02</v>
       </c>
       <c r="G159">
-        <v>0.37080000000000002</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H159">
         <v>1633.5000000000002</v>
@@ -31339,7 +31339,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
       <c r="G160">
-        <v>0.37080000000000002</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H160">
         <v>1633.5000000000005</v>
@@ -31392,7 +31392,7 @@
         <v>2.07E-2</v>
       </c>
       <c r="G161">
-        <v>0.37080000000000002</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H161">
         <v>1633.5000000000002</v>
@@ -31445,7 +31445,7 @@
         <v>8.1200000000000008E-2</v>
       </c>
       <c r="G162">
-        <v>0.37079999999999996</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H162">
         <v>1633.5</v>
@@ -31498,7 +31498,7 @@
         <v>0.02</v>
       </c>
       <c r="G163">
-        <v>0.37080000000000002</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H163">
         <v>1633.5000000000002</v>
@@ -31551,7 +31551,7 @@
         <v>5.04E-2</v>
       </c>
       <c r="G164">
-        <v>0.37080000000000002</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H164">
         <v>1391.4999999999998</v>
@@ -31604,7 +31604,7 @@
         <v>5.04E-2</v>
       </c>
       <c r="G165">
-        <v>0.37080000000000002</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H165">
         <v>1391.4999999999998</v>
@@ -31657,7 +31657,7 @@
         <v>0.05</v>
       </c>
       <c r="G166">
-        <v>0.37079999999999996</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H166">
         <v>1633.5000000000002</v>
@@ -31710,7 +31710,7 @@
         <v>0.05</v>
       </c>
       <c r="G167">
-        <v>0.37079999999999996</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H167">
         <v>1633.5000000000002</v>
@@ -31763,7 +31763,7 @@
         <v>0.05</v>
       </c>
       <c r="G168">
-        <v>0.37079999999999996</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H168">
         <v>1633.5000000000002</v>
@@ -31816,7 +31816,7 @@
         <v>0.05</v>
       </c>
       <c r="G169">
-        <v>0.37079999999999996</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H169">
         <v>1633.5000000000002</v>
@@ -31869,7 +31869,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="G170">
-        <v>0.34505000000000002</v>
+        <v>0.27604000000000001</v>
       </c>
       <c r="H170">
         <v>1782.0000000000002</v>
@@ -31922,7 +31922,7 @@
         <v>0.12</v>
       </c>
       <c r="G171">
-        <v>0.35535</v>
+        <v>0.28428000000000003</v>
       </c>
       <c r="H171">
         <v>1518.0000000000002</v>
@@ -32402,7 +32402,7 @@
         <v>191</v>
       </c>
       <c r="P180" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q180" t="s">
         <v>336</v>
@@ -32455,7 +32455,7 @@
         <v>191</v>
       </c>
       <c r="P181" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q181" t="s">
         <v>336</v>
@@ -32508,7 +32508,7 @@
         <v>193</v>
       </c>
       <c r="P182" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q182" t="s">
         <v>336</v>
@@ -32561,7 +32561,7 @@
         <v>193</v>
       </c>
       <c r="P183" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q183" t="s">
         <v>336</v>
@@ -32614,7 +32614,7 @@
         <v>195</v>
       </c>
       <c r="P184" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q184" t="s">
         <v>336</v>
@@ -32667,7 +32667,7 @@
         <v>195</v>
       </c>
       <c r="P185" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q185" t="s">
         <v>336</v>
@@ -32720,7 +32720,7 @@
         <v>197</v>
       </c>
       <c r="P186" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q186" t="s">
         <v>336</v>
@@ -32773,7 +32773,7 @@
         <v>197</v>
       </c>
       <c r="P187" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q187" t="s">
         <v>336</v>
@@ -32826,7 +32826,7 @@
         <v>199</v>
       </c>
       <c r="P188" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q188" t="s">
         <v>336</v>
@@ -32879,7 +32879,7 @@
         <v>199</v>
       </c>
       <c r="P189" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q189" t="s">
         <v>336</v>
@@ -32932,7 +32932,7 @@
         <v>200</v>
       </c>
       <c r="P190" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q190" t="s">
         <v>336</v>
@@ -32985,7 +32985,7 @@
         <v>200</v>
       </c>
       <c r="P191" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q191" t="s">
         <v>336</v>
@@ -33038,7 +33038,7 @@
         <v>201</v>
       </c>
       <c r="P192" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q192" t="s">
         <v>336</v>
@@ -33091,7 +33091,7 @@
         <v>201</v>
       </c>
       <c r="P193" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q193" t="s">
         <v>336</v>
@@ -33144,7 +33144,7 @@
         <v>203</v>
       </c>
       <c r="P194" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q194" t="s">
         <v>336</v>
@@ -33197,7 +33197,7 @@
         <v>203</v>
       </c>
       <c r="P195" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q195" t="s">
         <v>336</v>
@@ -33409,7 +33409,7 @@
         <v>209</v>
       </c>
       <c r="P199" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q199" t="s">
         <v>336</v>
@@ -33462,7 +33462,7 @@
         <v>209</v>
       </c>
       <c r="P200" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q200" t="s">
         <v>336</v>
@@ -33706,7 +33706,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="G205">
-        <v>0.19570000000000001</v>
+        <v>0.15656000000000003</v>
       </c>
       <c r="H205">
         <v>1336.5</v>
@@ -33759,7 +33759,7 @@
         <v>0.1</v>
       </c>
       <c r="G206">
-        <v>0.21629999999999999</v>
+        <v>0.17303999999999997</v>
       </c>
       <c r="H206">
         <v>1336.5</v>
@@ -33812,7 +33812,7 @@
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="G207">
-        <v>0.22660000000000002</v>
+        <v>0.18128</v>
       </c>
       <c r="H207">
         <v>1138.5</v>
@@ -33865,7 +33865,7 @@
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="G208">
-        <v>0.2472</v>
+        <v>0.19776000000000002</v>
       </c>
       <c r="H208">
         <v>1138.5</v>
@@ -33918,7 +33918,7 @@
         <v>0.05</v>
       </c>
       <c r="G209">
-        <v>0.29869999999999997</v>
+        <v>0.23895999999999998</v>
       </c>
       <c r="H209">
         <v>1336.5</v>
@@ -33971,7 +33971,7 @@
         <v>0.06</v>
       </c>
       <c r="G210">
-        <v>0.20600000000000002</v>
+        <v>0.16480000000000003</v>
       </c>
       <c r="H210">
         <v>1138.5</v>
@@ -34024,7 +34024,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G211">
-        <v>0.32445000000000002</v>
+        <v>0.25956000000000001</v>
       </c>
       <c r="H211">
         <v>1265</v>
@@ -34077,7 +34077,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G212">
-        <v>0.32445000000000002</v>
+        <v>0.25956000000000001</v>
       </c>
       <c r="H212">
         <v>1265</v>
@@ -34130,7 +34130,7 @@
         <v>7.2800000000000004E-2</v>
       </c>
       <c r="G213">
-        <v>0.29354999999999998</v>
+        <v>0.23483999999999999</v>
       </c>
       <c r="H213">
         <v>1265</v>
@@ -36355,7 +36355,7 @@
         <v>284</v>
       </c>
       <c r="P253" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q253" t="s">
         <v>336</v>
@@ -36411,7 +36411,7 @@
         <v>284</v>
       </c>
       <c r="P254" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q254" t="s">
         <v>336</v>
@@ -36859,7 +36859,7 @@
         <v>298</v>
       </c>
       <c r="P262" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q262" t="s">
         <v>336</v>
@@ -36915,7 +36915,7 @@
         <v>298</v>
       </c>
       <c r="P263" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q263" t="s">
         <v>336</v>
@@ -36971,7 +36971,7 @@
         <v>300</v>
       </c>
       <c r="P264" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q264" t="s">
         <v>336</v>
@@ -37027,7 +37027,7 @@
         <v>300</v>
       </c>
       <c r="P265" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q265" t="s">
         <v>336</v>
@@ -37195,7 +37195,7 @@
         <v>305</v>
       </c>
       <c r="P268" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q268" t="s">
         <v>336</v>
@@ -37251,7 +37251,7 @@
         <v>305</v>
       </c>
       <c r="P269" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q269" t="s">
         <v>336</v>
@@ -37307,7 +37307,7 @@
         <v>306</v>
       </c>
       <c r="P270" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q270" t="s">
         <v>336</v>
@@ -37363,7 +37363,7 @@
         <v>306</v>
       </c>
       <c r="P271" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q271" t="s">
         <v>336</v>
@@ -37587,7 +37587,7 @@
         <v>313</v>
       </c>
       <c r="P275" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q275" t="s">
         <v>336</v>
@@ -37643,7 +37643,7 @@
         <v>313</v>
       </c>
       <c r="P276" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q276" t="s">
         <v>336</v>
@@ -37699,7 +37699,7 @@
         <v>315</v>
       </c>
       <c r="P277" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="Q277" t="s">
         <v>336</v>
@@ -37755,7 +37755,7 @@
         <v>315</v>
       </c>
       <c r="P278" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q278" t="s">
         <v>336</v>
@@ -52089,7 +52089,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6008BEE9-E41A-40BF-B8D0-7FE859A1CEAF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50D674E0-B18A-4EFC-88FD-7B555894997D}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_GBR/vt_vervestacks_GBR_v1.xlsx
+++ b/VerveStacks_GBR/vt_vervestacks_GBR_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GBR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BBA84590-18F6-4B14-A920-131AF6AE716E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0BF9D68-AEBA-4F7A-8991-E59BABD296C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{17481CAD-3507-4AD2-90C4-3E8ABD688022}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A2A16D1A-BD66-41D1-9805-B8756B392E07}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1088,22 +1088,22 @@
     <t>ele</t>
   </si>
   <si>
+    <t>Aggregated Plant -- construction</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
     <t>Aggregated Plant -- operating</t>
-  </si>
-  <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>TWh</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Aggregated Plant -- construction</t>
   </si>
   <si>
     <t>Edmonton Ecopark power station_South -- construction</t>
@@ -4123,7 +4123,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7292F6E-D241-4CB4-857E-E857F0AA0907}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB4DB2D8-46F9-457C-AF8F-C24813074F11}">
   <dimension ref="B9:T169"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -13068,7 +13068,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{202545BB-90E5-43F4-916C-DEC4783D9347}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B302D9C1-016F-438A-8602-B9AACA7E17E3}">
   <dimension ref="B9:T213"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14999,6 +14999,9 @@
       <c r="G45">
         <v>0.33123000000000002</v>
       </c>
+      <c r="K45">
+        <v>30</v>
+      </c>
       <c r="N45" t="s">
         <v>348</v>
       </c>
@@ -16481,7 +16484,7 @@
         <v>7.5075000000000003</v>
       </c>
       <c r="K73">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="N73" t="s">
         <v>348</v>
@@ -16587,7 +16590,7 @@
         <v>7.5075000000000012</v>
       </c>
       <c r="K75">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="N75" t="s">
         <v>490</v>
@@ -24135,7 +24138,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0247D63E-492B-4CC8-965D-5C2C78CD2103}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40F277F8-6E1E-43BC-95F1-EF15AE74F80A}">
   <dimension ref="B9:T698"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26096,7 +26099,7 @@
         <v>49</v>
       </c>
       <c r="P46" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q46" t="s">
         <v>350</v>
@@ -26140,7 +26143,7 @@
         <v>9.240000000000002</v>
       </c>
       <c r="K47">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="N47" t="s">
         <v>348</v>
@@ -26193,7 +26196,7 @@
         <v>9.240000000000002</v>
       </c>
       <c r="K48">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="N48" t="s">
         <v>348</v>
@@ -26352,7 +26355,7 @@
         <v>5.25</v>
       </c>
       <c r="K51">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="N51" t="s">
         <v>348</v>
@@ -26405,7 +26408,7 @@
         <v>5.25</v>
       </c>
       <c r="K52">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="N52" t="s">
         <v>348</v>
@@ -26458,7 +26461,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="K53">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N53" t="s">
         <v>348</v>
@@ -26511,7 +26514,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="K54">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N54" t="s">
         <v>348</v>
@@ -27677,7 +27680,7 @@
         <v>3.1500000000000004</v>
       </c>
       <c r="K76">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="N76" t="s">
         <v>348</v>
@@ -27836,7 +27839,7 @@
         <v>3.1500000000000008</v>
       </c>
       <c r="K79">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="N79" t="s">
         <v>348</v>
@@ -27889,7 +27892,7 @@
         <v>3.1500000000000008</v>
       </c>
       <c r="K80">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="N80" t="s">
         <v>348</v>
@@ -29806,7 +29809,7 @@
         <v>120</v>
       </c>
       <c r="P116" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q116" t="s">
         <v>350</v>
@@ -30866,7 +30869,7 @@
         <v>140</v>
       </c>
       <c r="P136" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="Q136" t="s">
         <v>350</v>
@@ -30919,7 +30922,7 @@
         <v>140</v>
       </c>
       <c r="P137" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q137" t="s">
         <v>350</v>
@@ -31290,7 +31293,7 @@
         <v>147</v>
       </c>
       <c r="P144" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="Q144" t="s">
         <v>350</v>
@@ -31396,7 +31399,7 @@
         <v>149</v>
       </c>
       <c r="P146" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="Q146" t="s">
         <v>350</v>
@@ -31970,7 +31973,7 @@
         <v>4.620000000000001</v>
       </c>
       <c r="K157">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="N157" t="s">
         <v>348</v>
@@ -33251,7 +33254,7 @@
         <v>187</v>
       </c>
       <c r="P181" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q181" t="s">
         <v>350</v>
@@ -33444,6 +33447,9 @@
       <c r="G185">
         <v>0.33123000000000002</v>
       </c>
+      <c r="K185">
+        <v>33</v>
+      </c>
       <c r="N185" t="s">
         <v>348</v>
       </c>
@@ -33816,7 +33822,7 @@
         <v>203</v>
       </c>
       <c r="P192" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="Q192" t="s">
         <v>350</v>
@@ -33869,7 +33875,7 @@
         <v>203</v>
       </c>
       <c r="P193" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q193" t="s">
         <v>350</v>
@@ -34028,7 +34034,7 @@
         <v>207</v>
       </c>
       <c r="P196" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q196" t="s">
         <v>350</v>
@@ -34081,7 +34087,7 @@
         <v>207</v>
       </c>
       <c r="P197" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="Q197" t="s">
         <v>350</v>
@@ -34134,7 +34140,7 @@
         <v>209</v>
       </c>
       <c r="P198" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="Q198" t="s">
         <v>350</v>
@@ -34187,7 +34193,7 @@
         <v>209</v>
       </c>
       <c r="P199" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q199" t="s">
         <v>350</v>
@@ -34240,7 +34246,7 @@
         <v>211</v>
       </c>
       <c r="P200" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="Q200" t="s">
         <v>350</v>
@@ -34293,7 +34299,7 @@
         <v>211</v>
       </c>
       <c r="P201" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q201" t="s">
         <v>350</v>
@@ -34346,7 +34352,7 @@
         <v>213</v>
       </c>
       <c r="P202" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="Q202" t="s">
         <v>350</v>
@@ -34399,7 +34405,7 @@
         <v>213</v>
       </c>
       <c r="P203" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q203" t="s">
         <v>350</v>
@@ -34558,7 +34564,7 @@
         <v>215</v>
       </c>
       <c r="P206" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="Q206" t="s">
         <v>350</v>
@@ -34611,7 +34617,7 @@
         <v>215</v>
       </c>
       <c r="P207" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q207" t="s">
         <v>350</v>
@@ -34770,7 +34776,7 @@
         <v>219</v>
       </c>
       <c r="P210" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q210" t="s">
         <v>350</v>
@@ -34823,7 +34829,7 @@
         <v>221</v>
       </c>
       <c r="P211" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q211" t="s">
         <v>350</v>
@@ -34876,7 +34882,7 @@
         <v>221</v>
       </c>
       <c r="P212" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="Q212" t="s">
         <v>350</v>
@@ -34929,7 +34935,7 @@
         <v>223</v>
       </c>
       <c r="P213" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q213" t="s">
         <v>350</v>
@@ -34973,7 +34979,7 @@
         <v>4.2</v>
       </c>
       <c r="K214">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="N214" t="s">
         <v>348</v>
@@ -34982,7 +34988,7 @@
         <v>223</v>
       </c>
       <c r="P214" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="Q214" t="s">
         <v>350</v>
@@ -35026,7 +35032,7 @@
         <v>4.2</v>
       </c>
       <c r="K215">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="N215" t="s">
         <v>348</v>
@@ -35035,7 +35041,7 @@
         <v>225</v>
       </c>
       <c r="P215" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q215" t="s">
         <v>350</v>
@@ -35088,7 +35094,7 @@
         <v>227</v>
       </c>
       <c r="P216" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q216" t="s">
         <v>350</v>
@@ -35185,7 +35191,7 @@
         <v>4.2</v>
       </c>
       <c r="K218">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N218" t="s">
         <v>348</v>
@@ -35459,7 +35465,7 @@
         <v>239</v>
       </c>
       <c r="P223" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q223" t="s">
         <v>350</v>
@@ -35512,7 +35518,7 @@
         <v>241</v>
       </c>
       <c r="P224" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q224" t="s">
         <v>350</v>
@@ -35565,7 +35571,7 @@
         <v>243</v>
       </c>
       <c r="P225" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q225" t="s">
         <v>350</v>
@@ -35618,7 +35624,7 @@
         <v>245</v>
       </c>
       <c r="P226" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="Q226" t="s">
         <v>350</v>
@@ -35671,7 +35677,7 @@
         <v>246</v>
       </c>
       <c r="P227" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q227" t="s">
         <v>350</v>
@@ -35724,7 +35730,7 @@
         <v>248</v>
       </c>
       <c r="P228" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q228" t="s">
         <v>350</v>
@@ -35758,6 +35764,9 @@
       <c r="G229">
         <v>0.33123000000000002</v>
       </c>
+      <c r="K229">
+        <v>33</v>
+      </c>
       <c r="L229">
         <v>0.14522090101425866</v>
       </c>
@@ -35768,7 +35777,7 @@
         <v>250</v>
       </c>
       <c r="P229" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q229" t="s">
         <v>350</v>
@@ -35802,6 +35811,9 @@
       <c r="G230">
         <v>0.33123000000000002</v>
       </c>
+      <c r="K230">
+        <v>33</v>
+      </c>
       <c r="L230">
         <v>0.14522090101425866</v>
       </c>
@@ -35812,7 +35824,7 @@
         <v>252</v>
       </c>
       <c r="P230" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q230" t="s">
         <v>350</v>
@@ -35846,6 +35858,9 @@
       <c r="G231">
         <v>0.33123000000000002</v>
       </c>
+      <c r="K231">
+        <v>33</v>
+      </c>
       <c r="L231">
         <v>0.14522090101425866</v>
       </c>
@@ -37760,7 +37775,7 @@
         <v>294</v>
       </c>
       <c r="P265" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q265" t="s">
         <v>350</v>
@@ -37816,7 +37831,7 @@
         <v>296</v>
       </c>
       <c r="P266" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q266" t="s">
         <v>350</v>
@@ -37872,7 +37887,7 @@
         <v>298</v>
       </c>
       <c r="P267" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="Q267" t="s">
         <v>350</v>
@@ -37928,7 +37943,7 @@
         <v>298</v>
       </c>
       <c r="P268" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q268" t="s">
         <v>350</v>
@@ -37984,7 +37999,7 @@
         <v>300</v>
       </c>
       <c r="P269" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q269" t="s">
         <v>350</v>
@@ -38040,7 +38055,7 @@
         <v>302</v>
       </c>
       <c r="P270" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q270" t="s">
         <v>350</v>
@@ -38096,7 +38111,7 @@
         <v>304</v>
       </c>
       <c r="P271" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q271" t="s">
         <v>350</v>
@@ -38152,7 +38167,7 @@
         <v>306</v>
       </c>
       <c r="P272" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q272" t="s">
         <v>350</v>
@@ -38208,7 +38223,7 @@
         <v>308</v>
       </c>
       <c r="P273" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q273" t="s">
         <v>350</v>
@@ -38376,7 +38391,7 @@
         <v>312</v>
       </c>
       <c r="P276" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q276" t="s">
         <v>350</v>
@@ -38432,7 +38447,7 @@
         <v>312</v>
       </c>
       <c r="P277" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="Q277" t="s">
         <v>350</v>
@@ -38600,7 +38615,7 @@
         <v>315</v>
       </c>
       <c r="P280" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q280" t="s">
         <v>350</v>
@@ -38656,7 +38671,7 @@
         <v>317</v>
       </c>
       <c r="P281" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q281" t="s">
         <v>350</v>
@@ -38824,7 +38839,7 @@
         <v>320</v>
       </c>
       <c r="P284" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="Q284" t="s">
         <v>350</v>
@@ -38880,7 +38895,7 @@
         <v>320</v>
       </c>
       <c r="P285" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q285" t="s">
         <v>350</v>
@@ -38936,7 +38951,7 @@
         <v>321</v>
       </c>
       <c r="P286" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q286" t="s">
         <v>350</v>
@@ -38992,7 +39007,7 @@
         <v>323</v>
       </c>
       <c r="P287" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q287" t="s">
         <v>350</v>
@@ -39048,7 +39063,7 @@
         <v>325</v>
       </c>
       <c r="P288" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q288" t="s">
         <v>350</v>
@@ -39104,7 +39119,7 @@
         <v>327</v>
       </c>
       <c r="P289" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="Q289" t="s">
         <v>350</v>
@@ -39160,7 +39175,7 @@
         <v>327</v>
       </c>
       <c r="P290" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q290" t="s">
         <v>350</v>
@@ -41861,8 +41876,11 @@
       <c r="G360">
         <v>0.33123000000000002</v>
       </c>
+      <c r="K360">
+        <v>33</v>
+      </c>
       <c r="L360">
-        <v>0.55373821771400944</v>
+        <v>0.55373821771400933</v>
       </c>
     </row>
     <row r="361" spans="2:12" x14ac:dyDescent="0.45">
@@ -41884,8 +41902,11 @@
       <c r="G361">
         <v>0.33123000000000002</v>
       </c>
+      <c r="K361">
+        <v>33</v>
+      </c>
       <c r="L361">
-        <v>0.55373821771400944</v>
+        <v>0.55373821771400933</v>
       </c>
     </row>
     <row r="362" spans="2:12" x14ac:dyDescent="0.45">
@@ -41907,8 +41928,11 @@
       <c r="G362">
         <v>0.33123000000000002</v>
       </c>
+      <c r="K362">
+        <v>33</v>
+      </c>
       <c r="L362">
-        <v>0.55373821771400944</v>
+        <v>0.55373821771400933</v>
       </c>
     </row>
     <row r="363" spans="2:12" x14ac:dyDescent="0.45">
@@ -43785,6 +43809,9 @@
       <c r="G416">
         <v>0.33123000000000002</v>
       </c>
+      <c r="K416">
+        <v>33</v>
+      </c>
       <c r="L416">
         <v>0.49119628387312647</v>
       </c>
@@ -43808,6 +43835,9 @@
       <c r="G417">
         <v>0.33123000000000002</v>
       </c>
+      <c r="K417">
+        <v>33</v>
+      </c>
       <c r="L417">
         <v>0.49119628387312647</v>
       </c>
@@ -43830,6 +43860,9 @@
       </c>
       <c r="G418">
         <v>0.33123000000000002</v>
+      </c>
+      <c r="K418">
+        <v>33</v>
       </c>
       <c r="L418">
         <v>0.49119628387312647</v>
@@ -53641,7 +53674,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B78933-00AA-4BD1-9F6A-9A12DB73DC56}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63D54B38-6FE3-4039-96F0-12A7099A1519}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
